--- a/storage/app/python/datasets/tempat_makan_clean.xlsx
+++ b/storage/app/python/datasets/tempat_makan_clean.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/prom4/Documents/GITHUB/Malang-Raya/storage/app/python/datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1D4C8D-B795-5E4C-97F1-24FBD7B5E39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{607E6243-EF2F-934E-AB80-52607047C4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7220" yWindow="4860" windowWidth="23020" windowHeight="14780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9130,6 +9130,7 @@
   <dimension ref="A1:R640"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="2" max="2" width="89.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="200" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
@@ -15536,7 +15537,7 @@
         <v>2909</v>
       </c>
       <c r="F115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G115">
         <v>-7.9001776000000001</v>
@@ -21640,7 +21641,7 @@
         <v>2909</v>
       </c>
       <c r="F224">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G224">
         <v>-7.8225496000000003</v>
@@ -24888,7 +24889,7 @@
         <v>2909</v>
       </c>
       <c r="F282">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G282">
         <v>-8.1296640999999994</v>
@@ -25112,7 +25113,7 @@
         <v>2909</v>
       </c>
       <c r="F286">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G286">
         <v>-8.1292030999999998</v>
@@ -41632,7 +41633,7 @@
         <v>2909</v>
       </c>
       <c r="F581">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G581">
         <v>-8.2099259999999994</v>
@@ -44656,7 +44657,7 @@
         <v>2909</v>
       </c>
       <c r="F635">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G635">
         <v>-8.2298741</v>
@@ -44824,7 +44825,7 @@
         <v>2909</v>
       </c>
       <c r="F638">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G638">
         <v>-8.0136389999999995</v>
@@ -44880,7 +44881,7 @@
         <v>2909</v>
       </c>
       <c r="F639">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G639">
         <v>-8.0153026999999994</v>
@@ -44976,6 +44977,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R640">
+    <sortCondition ref="A2:A640"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>